--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-organization.xlsx
@@ -364,7 +364,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -679,7 +679,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -944,7 +944,7 @@
     <t>組織を分類するために使用されます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1576,7 +1576,7 @@
     <t>「連絡を取りたい目的のための連絡先」となります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1643,7 +1643,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
